--- a/data/trans_camb/P19-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 13,15</t>
+          <t>-1,08; 13,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 17,68</t>
+          <t>2,91; 18,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,43; 26,38</t>
+          <t>8,87; 25,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 11,9</t>
+          <t>-3,23; 12,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 20,22</t>
+          <t>4,2; 19,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 24,02</t>
+          <t>9,57; 23,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,6</t>
+          <t>-0,1; 10,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 17,17</t>
+          <t>5,93; 16,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 22,71</t>
+          <t>11,17; 22,45</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 82,68</t>
+          <t>-4,19; 80,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 108,23</t>
+          <t>12,08; 108,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39,66; 163,83</t>
+          <t>37,91; 152,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,01; 63,52</t>
+          <t>-11,86; 62,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,21; 106,21</t>
+          <t>15,97; 106,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,26; 129,13</t>
+          <t>34,64; 124,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 55,02</t>
+          <t>-0,67; 54,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,5; 93,21</t>
+          <t>23,84; 92,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>47,23; 122,92</t>
+          <t>45,71; 120,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 1,28</t>
+          <t>-10,93; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 5,31</t>
+          <t>-6,65; 5,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 2,33</t>
+          <t>-10,53; 2,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,97; -4,0</t>
+          <t>-15,37; -3,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 3,33</t>
+          <t>-8,79; 3,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,43; -2,27</t>
+          <t>-13,4; -2,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -2,57</t>
+          <t>-10,62; -2,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 2,57</t>
+          <t>-5,67; 2,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,37; -1,62</t>
+          <t>-10,55; -2,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 4,97</t>
+          <t>-33,32; 5,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 21,04</t>
+          <t>-20,41; 21,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 9,32</t>
+          <t>-34,03; 11,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -12,27</t>
+          <t>-40,82; -12,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 10,08</t>
+          <t>-22,75; 9,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -7,16</t>
+          <t>-35,04; -7,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,65; -8,7</t>
+          <t>-31,28; -9,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 8,89</t>
+          <t>-16,64; 9,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,59; -5,17</t>
+          <t>-30,96; -6,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 7,14</t>
+          <t>-5,53; 7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 14,19</t>
+          <t>0,21; 13,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 4,12</t>
+          <t>-7,76; 4,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 14,72</t>
+          <t>0,53; 14,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 9,98</t>
+          <t>-4,41; 9,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 8,06</t>
+          <t>-3,63; 8,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 9,76</t>
+          <t>-0,17; 9,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 10,31</t>
+          <t>0,39; 10,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 5,45</t>
+          <t>-4,05; 4,7</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 38,1</t>
+          <t>-21,54; 40,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 75,26</t>
+          <t>0,8; 72,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,92; 21,4</t>
+          <t>-31,68; 24,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 60,14</t>
+          <t>2,07; 60,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 39,14</t>
+          <t>-14,66; 40,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 32,65</t>
+          <t>-11,68; 37,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 43,32</t>
+          <t>-0,94; 41,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 46,09</t>
+          <t>1,26; 43,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 24,18</t>
+          <t>-14,69; 20,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 6,57</t>
+          <t>-6,25; 7,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 10,99</t>
+          <t>-2,17; 11,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 20,7</t>
+          <t>3,78; 20,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 0,4</t>
+          <t>-13,84; -0,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 12,2</t>
+          <t>-1,9; 12,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 21,57</t>
+          <t>-6,51; 20,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 1,36</t>
+          <t>-8,19; 1,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 9,64</t>
+          <t>-0,21; 9,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 18,22</t>
+          <t>-0,71; 18,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 27,8</t>
+          <t>-21,07; 30,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 47,2</t>
+          <t>-7,22; 51,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,04; 88,01</t>
+          <t>13,13; 89,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,44; 1,28</t>
+          <t>-37,85; -1,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 41,97</t>
+          <t>-5,23; 43,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 70,03</t>
+          <t>-19,09; 66,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 5,17</t>
+          <t>-24,77; 4,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 34,69</t>
+          <t>-0,64; 35,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,01; 64,24</t>
+          <t>-2,2; 65,42</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -4,72</t>
+          <t>-22,56; -5,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-24,95; -8,62</t>
+          <t>-25,53; -9,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-29,0; -13,94</t>
+          <t>-28,34; -13,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 13,45</t>
+          <t>-3,98; 12,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 6,58</t>
+          <t>-10,99; 5,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,11; -4,15</t>
+          <t>-18,55; -3,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 1,76</t>
+          <t>-11,24; 1,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -3,83</t>
+          <t>-16,0; -3,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-21,25; -10,67</t>
+          <t>-20,55; -10,05</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,42; -16,42</t>
+          <t>-60,23; -17,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-66,1; -28,52</t>
+          <t>-67,08; -31,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,51; -46,82</t>
+          <t>-75,59; -47,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 57,7</t>
+          <t>-12,2; 52,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 28,37</t>
+          <t>-33,28; 22,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-52,36; -14,56</t>
+          <t>-54,12; -14,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 7,03</t>
+          <t>-32,86; 4,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,56; -13,77</t>
+          <t>-46,27; -11,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,68; -37,24</t>
+          <t>-59,89; -36,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,05; 18,17</t>
+          <t>3,64; 18,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8,28; 23,94</t>
+          <t>7,76; 22,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 11,35</t>
+          <t>-2,95; 11,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 3,76</t>
+          <t>-11,55; 3,98</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 14,84</t>
+          <t>-1,53; 15,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 0,87</t>
+          <t>-12,95; 1,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,42</t>
+          <t>-2,25; 8,9</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,6; 16,77</t>
+          <t>5,34; 16,37</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 4,59</t>
+          <t>-5,82; 4,09</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,86; 112,68</t>
+          <t>15,74; 115,87</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35,24; 148,14</t>
+          <t>33,66; 142,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 67,12</t>
+          <t>-13,26; 66,23</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,88; 12,65</t>
+          <t>-30,95; 12,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 50,4</t>
+          <t>-3,88; 49,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 2,96</t>
+          <t>-34,24; 5,27</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 33,26</t>
+          <t>-7,73; 35,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18,66; 68,03</t>
+          <t>17,16; 66,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 19,35</t>
+          <t>-19,48; 17,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 0,77</t>
+          <t>-9,45; 0,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,56</t>
+          <t>-6,06; 4,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 11,36</t>
+          <t>0,09; 11,69</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 0,48</t>
+          <t>-9,44; 1,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,07</t>
+          <t>-5,93; 5,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 3,05</t>
+          <t>-24,27; 3,29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -0,58</t>
+          <t>-7,86; -0,52</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,88</t>
+          <t>-4,6; 3,01</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 5,34</t>
+          <t>-15,22; 4,81</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,74; 2,68</t>
+          <t>-30,37; 1,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,84; 17,69</t>
+          <t>-19,07; 15,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 42,5</t>
+          <t>0,29; 43,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 1,63</t>
+          <t>-23,37; 3,3</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 11,95</t>
+          <t>-14,81; 14,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 7,99</t>
+          <t>-60,12; 8,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,48; -1,91</t>
+          <t>-22,52; -1,66</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 9,04</t>
+          <t>-13,0; 9,45</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 16,0</t>
+          <t>-44,89; 14,47</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,07</t>
+          <t>-1,47; 7,22</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,59; 13,4</t>
+          <t>4,62; 13,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 0,53</t>
+          <t>-15,22; 0,1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 8,95</t>
+          <t>-0,06; 8,99</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,24</t>
+          <t>2,35; 11,88</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 2,06</t>
+          <t>-6,79; 1,59</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,97</t>
+          <t>0,45; 6,84</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,56; 11,38</t>
+          <t>4,84; 11,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -0,71</t>
+          <t>-13,05; -0,86</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 37,01</t>
+          <t>-6,45; 39,67</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>20,21; 72,76</t>
+          <t>20,15; 72,62</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-70,67; 2,74</t>
+          <t>-67,97; 0,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 37,81</t>
+          <t>-0,81; 37,13</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,45; 46,39</t>
+          <t>8,38; 48,58</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 8,3</t>
+          <t>-23,25; 6,61</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,57; 32,27</t>
+          <t>1,76; 31,27</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,81; 51,51</t>
+          <t>18,75; 49,94</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-52,96; -3,18</t>
+          <t>-51,64; -3,59</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,0</t>
+          <t>-2,31; 2,0</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,63</t>
+          <t>2,09; 6,41</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 3,23</t>
+          <t>-5,32; 3,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,4</t>
+          <t>-3,33; 1,24</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,43</t>
+          <t>0,88; 5,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 1,87</t>
+          <t>-7,14; 1,68</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,12</t>
+          <t>-2,06; 0,96</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,35</t>
+          <t>2,07; 5,26</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,62</t>
+          <t>-4,41; 1,67</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 8,5</t>
+          <t>-9,0; 8,38</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7,74; 27,76</t>
+          <t>7,97; 26,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,64; 13,16</t>
+          <t>-20,55; 13,1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 4,68</t>
+          <t>-10,3; 4,17</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,79; 18,19</t>
+          <t>2,66; 18,04</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-23,14; 6,12</t>
+          <t>-22,18; 5,39</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 4,08</t>
+          <t>-7,12; 3,46</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>6,48; 19,46</t>
+          <t>7,11; 19,09</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 5,82</t>
+          <t>-15,29; 6,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P19-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,53</t>
+          <t>15,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,05</t>
+          <t>15,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,28</t>
+          <t>15,09</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 13,0</t>
+          <t>-0,92; 12,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 18,1</t>
+          <t>3,12; 17,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 25,64</t>
+          <t>8,49; 22,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 12,18</t>
+          <t>-3,7; 10,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 19,47</t>
+          <t>3,68; 19,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,57; 23,59</t>
+          <t>7,73; 22,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 10,25</t>
+          <t>-0,21; 9,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 16,82</t>
+          <t>6,52; 17,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 22,45</t>
+          <t>10,27; 19,64</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>71,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 80,27</t>
+          <t>-3,97; 75,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 108,69</t>
+          <t>11,29; 104,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,91; 152,04</t>
+          <t>33,17; 131,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 62,84</t>
+          <t>-14,88; 57,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,97; 106,19</t>
+          <t>13,25; 104,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,64; 124,42</t>
+          <t>27,44; 127,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 54,06</t>
+          <t>-0,58; 53,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,84; 92,39</t>
+          <t>27,79; 92,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>45,71; 120,89</t>
+          <t>43,3; 107,53</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-5,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,0</t>
+          <t>-8,15</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-6,13</t>
+          <t>-6,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 1,48</t>
+          <t>-9,89; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 5,49</t>
+          <t>-6,75; 5,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 2,63</t>
+          <t>-11,54; 0,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -3,93</t>
+          <t>-15,06; -3,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 3,07</t>
+          <t>-8,56; 3,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; -2,37</t>
+          <t>-13,45; -2,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -2,67</t>
+          <t>-11,06; -2,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 2,89</t>
+          <t>-5,97; 2,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; -2,13</t>
+          <t>-10,35; -2,15</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-14,59%</t>
+          <t>-17,47%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,88%</t>
+          <t>-23,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-19,24%</t>
+          <t>-20,7%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 5,86</t>
+          <t>-30,75; 7,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 21,05</t>
+          <t>-21,13; 20,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,03; 11,35</t>
+          <t>-36,36; 2,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-40,82; -12,07</t>
+          <t>-40,27; -10,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 9,59</t>
+          <t>-23,47; 9,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; -7,73</t>
+          <t>-35,29; -8,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -9,12</t>
+          <t>-32,37; -8,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 9,39</t>
+          <t>-17,3; 8,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,96; -6,71</t>
+          <t>-31,08; -7,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,22</t>
+          <t>2,27</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 7,77</t>
+          <t>-6,12; 7,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 13,89</t>
+          <t>0,73; 13,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 4,49</t>
+          <t>-7,82; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 14,46</t>
+          <t>0,62; 14,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,82</t>
+          <t>-4,35; 9,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 8,89</t>
+          <t>-3,53; 9,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 9,49</t>
+          <t>-0,5; 9,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 10,19</t>
+          <t>0,42; 10,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 4,7</t>
+          <t>-4,58; 4,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-8,28%</t>
+          <t>-7,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 40,62</t>
+          <t>-23,24; 42,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,8; 72,27</t>
+          <t>2,84; 71,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 24,87</t>
+          <t>-30,98; 23,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 60,24</t>
+          <t>1,62; 57,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 40,05</t>
+          <t>-13,49; 38,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 37,52</t>
+          <t>-11,71; 36,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 41,26</t>
+          <t>-1,8; 40,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 43,46</t>
+          <t>1,53; 46,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 20,51</t>
+          <t>-15,87; 21,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12,18</t>
+          <t>9,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,37</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>10,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 7,19</t>
+          <t>-6,51; 7,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 11,78</t>
+          <t>-2,59; 11,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,78; 20,7</t>
+          <t>2,22; 18,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -0,63</t>
+          <t>-13,69; -0,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 12,24</t>
+          <t>-2,27; 11,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 20,99</t>
+          <t>3,21; 17,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 1,17</t>
+          <t>-8,24; 1,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,71</t>
+          <t>-0,18; 9,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 18,71</t>
+          <t>5,18; 15,62</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 30,91</t>
+          <t>-22,29; 31,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 51,74</t>
+          <t>-8,4; 48,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,13; 89,23</t>
+          <t>6,69; 76,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,85; -1,67</t>
+          <t>-37,46; -1,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 43,01</t>
+          <t>-6,13; 39,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,09; 66,15</t>
+          <t>8,48; 56,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 4,36</t>
+          <t>-25,72; 5,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 35,16</t>
+          <t>-0,81; 34,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 65,42</t>
+          <t>16,1; 56,77</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-21,19</t>
+          <t>-21,88</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-10,92</t>
+          <t>-11,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-15,83</t>
+          <t>-16,54</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-22,56; -5,16</t>
+          <t>-22,96; -5,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,53; -9,26</t>
+          <t>-25,43; -9,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,34; -13,65</t>
+          <t>-29,34; -14,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 12,86</t>
+          <t>-5,84; 12,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 5,57</t>
+          <t>-11,67; 5,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,55; -3,61</t>
+          <t>-18,21; -4,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 1,28</t>
+          <t>-11,15; 1,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-16,0; -3,33</t>
+          <t>-15,8; -3,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -10,05</t>
+          <t>-21,61; -11,36</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-63,29%</t>
+          <t>-65,37%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-37,83%</t>
+          <t>-39,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-50,81%</t>
+          <t>-53,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,23; -17,79</t>
+          <t>-60,34; -19,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-67,08; -31,04</t>
+          <t>-65,98; -28,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,59; -47,21</t>
+          <t>-77,04; -49,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 52,57</t>
+          <t>-16,95; 51,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 22,75</t>
+          <t>-35,02; 22,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,12; -14,34</t>
+          <t>-54,14; -19,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 4,59</t>
+          <t>-32,7; 5,59</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-46,27; -11,55</t>
+          <t>-45,56; -12,26</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-59,89; -36,61</t>
+          <t>-63,07; -41,09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>3,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-5,78</t>
+          <t>-6,08</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-1,39</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,64; 18,45</t>
+          <t>3,06; 19,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,76; 22,99</t>
+          <t>8,38; 23,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 11,02</t>
+          <t>-3,09; 10,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,98</t>
+          <t>-11,64; 4,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 15,14</t>
+          <t>-1,3; 15,53</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 1,5</t>
+          <t>-14,15; 0,94</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 8,9</t>
+          <t>-2,12; 8,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,34; 16,37</t>
+          <t>6,22; 16,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,09</t>
+          <t>-6,17; 3,62</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-16,81%</t>
+          <t>-17,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-2,8%</t>
+          <t>-5,14%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15,74; 115,87</t>
+          <t>14,14; 113,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>33,66; 142,05</t>
+          <t>33,11; 147,06</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 66,23</t>
+          <t>-13,36; 65,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,95; 12,64</t>
+          <t>-31,39; 13,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 49,7</t>
+          <t>-3,94; 50,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 5,27</t>
+          <t>-36,05; 2,87</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 35,93</t>
+          <t>-7,49; 34,6</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17,16; 66,25</t>
+          <t>20,82; 69,95</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 17,46</t>
+          <t>-20,9; 14,72</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>5,85</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-8,32</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,34</t>
+          <t>-9,47; 0,61</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 4,14</t>
+          <t>-5,51; 5,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 11,69</t>
+          <t>0,37; 11,32</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 1,23</t>
+          <t>-9,52; 1,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,03</t>
+          <t>-6,16; 4,56</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 3,29</t>
+          <t>-4,09; 5,4</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-7,86; -0,52</t>
+          <t>-8,02; -1,06</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,01</t>
+          <t>-4,15; 3,23</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 4,81</t>
+          <t>-0,51; 6,82</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-21,83%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-4,98%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 1,91</t>
+          <t>-30,53; 2,24</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 15,76</t>
+          <t>-17,77; 20,12</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,29; 43,55</t>
+          <t>1,26; 43,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 3,3</t>
+          <t>-23,47; 4,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 14,39</t>
+          <t>-14,82; 12,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,12; 8,54</t>
+          <t>-9,99; 15,29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,52; -1,66</t>
+          <t>-22,8; -3,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 9,45</t>
+          <t>-11,88; 9,93</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 14,47</t>
+          <t>-1,49; 21,54</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-6,18</t>
+          <t>-1,21</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,47</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,02</t>
+          <t>-2,12</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 7,22</t>
+          <t>-1,49; 6,84</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,62; 13,44</t>
+          <t>4,51; 13,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 0,1</t>
+          <t>-5,46; 2,94</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 8,99</t>
+          <t>-0,41; 8,65</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,35; 11,88</t>
+          <t>2,27; 11,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 1,59</t>
+          <t>-7,26; 0,92</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,84</t>
+          <t>0,46; 6,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,18</t>
+          <t>4,82; 11,39</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,05; -0,86</t>
+          <t>-5,14; 0,8</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-29,71%</t>
+          <t>-5,82%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-9,31%</t>
+          <t>-11,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-21,11%</t>
+          <t>-8,92%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 39,67</t>
+          <t>-6,59; 36,91</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>20,15; 72,62</t>
+          <t>19,7; 70,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 0,49</t>
+          <t>-23,48; 15,63</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 37,13</t>
+          <t>-1,76; 35,68</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,38; 48,58</t>
+          <t>7,33; 47,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 6,61</t>
+          <t>-25,4; 3,81</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,76; 31,27</t>
+          <t>1,97; 29,85</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>18,75; 49,94</t>
+          <t>18,74; 51,19</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,64; -3,59</t>
+          <t>-19,97; 3,72</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>0,63</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,0</t>
+          <t>-2,65; 2,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,41</t>
+          <t>1,81; 6,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,2</t>
+          <t>-1,09; 3,49</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,24</t>
+          <t>-3,16; 1,24</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,43</t>
+          <t>0,89; 5,37</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,68</t>
+          <t>-2,35; 1,83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,96</t>
+          <t>-2,21; 0,98</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,26</t>
+          <t>2,01; 5,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,67</t>
+          <t>-0,81; 2,22</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-4,71%</t>
+          <t>-0,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 8,38</t>
+          <t>-10,05; 8,54</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>7,97; 26,84</t>
+          <t>7,02; 26,74</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 13,1</t>
+          <t>-4,2; 14,61</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 4,17</t>
+          <t>-9,7; 4,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>2,66; 18,04</t>
+          <t>2,66; 17,83</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-22,18; 5,39</t>
+          <t>-7,18; 6,03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,46</t>
+          <t>-7,69; 3,5</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>7,11; 19,09</t>
+          <t>6,82; 19,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 6,12</t>
+          <t>-2,77; 8,14</t>
         </is>
       </c>
     </row>
